--- a/bench/data/files/synthetic6_B.xlsx
+++ b/bench/data/files/synthetic6_B.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Kepler Holdings</t>
+          <t>Echo Partners</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -581,52 +581,52 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2012-12-14</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>804.6</v>
+        <v>1292</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>842.6</v>
+        <v>3969</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>139.6</v>
+        <v>312.1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>336.8</v>
+        <v>493.7</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>535.6</v>
+        <v>348.2</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.68</v>
+        <v>0.249</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>James Hassan; Sophie Brown</t>
+          <t>Thomas Zhang; Jennifer Zhang</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Vertex AG</t>
+          <t>Cobalt Logic</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -636,52 +636,52 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2010-03-20</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2014-04-16</t>
+          <t>2015-06-07</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1734.1</v>
+        <v>220.5</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2701.4</v>
+        <v>713</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>165.5</v>
+        <v>38.8</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>353.4</v>
+        <v>89.5</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>569</v>
+        <v>147.2</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.381</v>
+        <v>0.419</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Jessica Chen; Laura Nakamura; Robert Ueno; Thomas Ueno; Jessica Tanaka</t>
+          <t>Ahmed Tanaka; Ahmed Chen; James Nakamura; Priya Mueller; James Evans</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Atlas Labs</t>
+          <t>Helix Solutions</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -691,42 +691,42 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2011-12-17</t>
+          <t>2013-04-22</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2017-03-14</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1341</v>
+        <v>1128</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1684.4</v>
+        <v>3111.7</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>146.7</v>
+        <v>255.8</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>178.5</v>
+        <v>475.8</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>583.5</v>
+        <v>695.5</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.878</v>
+        <v>0.907</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Hannah Kim; Jessica Qureshi</t>
+          <t>Elena Mueller; Rachel Kim; Laura Schmidt; Wei Evans</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Nimbus Logistics</t>
+          <t>Drift Media</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -746,35 +746,35 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2010-04-08</t>
+          <t>2012-03-07</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2017-04-08</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>100.7</v>
+        <v>1549.1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>120.3</v>
+        <v>3787.4</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>13.6</v>
+        <v>155.6</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>23.4</v>
+        <v>388.4</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>60.5</v>
+        <v>534.3</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.648</v>
+        <v>0.949</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Andrew Johnson; Amanda Johnson; Priya Ueno; Elena Vega; Sophie Vega</t>
+          <t>Sarah Schmidt; Thomas Rossi; Mark Gupta; Christopher O'Brien</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Delta Pharma</t>
+          <t>Lumen Ltd</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -808,103 +808,107 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2012-05-18</t>
+          <t>2013-02-14</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2018-03-26</t>
+          <t>2016-11-26</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1197.1</v>
+        <v>1937.2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1796.6</v>
+        <v>6518.1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>199.7</v>
+        <v>294</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>271</v>
+        <v>728.1</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>211.5</v>
+        <v>240.7</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.868</v>
+        <v>0.387</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Michael Williams; Matthew Kim; Ahmed Yamamoto; Mark Patel</t>
+          <t>Daniel Yamamoto; Jennifer Lopez; Emma Zhang; Olivia Tanaka</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Lattice Capital</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>2013-01-05</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2021-02-20</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="n">
-        <v>912.9</v>
+        <v>1944.7</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v/>
+        <v>2562.9</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>155.6</v>
+        <v>225.9</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v/>
+        <v>540.1</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>151.8</v>
+        <v>558.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.307</v>
+        <v>0.576</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Robert Schmidt; Sophie Xu</t>
+          <t>James Evans; Olivia Williams; Ahmed Davis</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Umbra Labs</t>
+          <t>Vertex Industries</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -914,42 +918,42 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
+          <t>2013-07-17</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2017-04-20</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>287.5</v>
+        <v>499.8</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>217.5</v>
+        <v>1347</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>30.3</v>
+        <v>107.2</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>35.4</v>
+        <v>144.6</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>100</v>
+        <v>480.7</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.881</v>
+        <v>0.331</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Jessica Evans; Elena Qureshi; James Evans; Andrew Ivanov; Andrew O'Brien</t>
+          <t>Mark Rossi; Wei Chen; Hannah Gupta; Amanda Rossi; Jessica Lopez</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Atlas Corp</t>
+          <t>Helix Tech</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -959,7 +963,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -969,158 +973,114 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2013-12-26</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2018-04-29</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1546.7</v>
+        <v>1896.4</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>3140</v>
+        <v>3156.8</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>209.5</v>
+        <v>316</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>401.8</v>
+        <v>653.6</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>142.3</v>
+        <v>876.1</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.399</v>
+        <v>0.318</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Chen; Ravi Xu; James Vega; Hannah Brown; Michael Chen</t>
+          <t>Robert Hassan; Ahmed Zhang; David Evans</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Systems</t>
+          <t>Krypton Health</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2013-01-20</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr"/>
+          <t>2013-01-22</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-19</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="n">
-        <v>463.6</v>
+        <v>1624.2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v/>
+        <v>5603.8</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>397.8</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v/>
+        <v>948.8</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>110.4</v>
+        <v>296.3</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.707</v>
+        <v>0.823</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Sophie Ivanov; Elena Lopez</t>
+          <t>Sarah Ivanov; Yuki Patel; Laura Tanaka; Christopher Mueller</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Ember Pharma</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2014-08-23</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>1684.2</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>4581.1</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>334.7</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>814.1</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>231</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Ahmed Ivanov; Michael Lopez; Matthew Vega</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Fund C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Tessera Materials</t>
+          <t>Forge Industries</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1130,52 +1090,52 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
+          <t>2016-02-05</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1738.3</v>
+        <v>567.9</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>3202.1</v>
+        <v>1874.8</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>152.2</v>
+        <v>124.2</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>132.7</v>
+        <v>275.9</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>430.9</v>
+        <v>500.4</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.263</v>
+        <v>0.863</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Andrew Ivanov; Sophie Ivanov; James Anderson; Andrew Schmidt</t>
+          <t>Yuki Johnson; Hannah Rossi; Laura Johnson</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Bio</t>
+          <t>Kepler Group</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1185,54 +1145,102 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2013-01-08</t>
+          <t>2016-03-21</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2017-10-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>294.7</v>
+        <v>1176.3</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>761.4</v>
+        <v>1834.6</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>60.6</v>
+        <v>172.7</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>88.90000000000001</v>
+        <v>145.4</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>47.9</v>
+        <v>217.5</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.361</v>
+        <v>0.245</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Christopher Gupta; Priya Patel; James Fischer; Sarah Hassan</t>
+          <t>Yuki Evans; Thomas Evans; Sophie Nakamura; Sarah Lopez</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Fund C</t>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Apex Health</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2017-12-05</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2021-01-31</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1989.3</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>3819</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>495.1</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>675.2</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Jennifer Fischer; Matthew Patel</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Zenith Media</t>
+          <t>Halo AG</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1247,52 +1255,52 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>524.2</v>
+        <v>988</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1200.3</v>
+        <v>2070.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>124.9</v>
+        <v>232.6</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>207.2</v>
+        <v>553.3</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>245.7</v>
+        <v>750.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.956</v>
+        <v>0.931</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Thomas Lopez; Ahmed Brown; James Williams</t>
+          <t>Andrew Chen; Robert Schmidt; Thomas Gupta; Elena Qureshi</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Materials</t>
+          <t>Meridian Industries</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1302,52 +1310,52 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1747.7</v>
+        <v>991.2</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4987.8</v>
+        <v>1571.7</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>197.8</v>
+        <v>152.8</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>481.4</v>
+        <v>376.1</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>677.4</v>
+        <v>516.9</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.749</v>
+        <v>0.411</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>James Chen; Christopher Williams</t>
+          <t>Robert Anderson; Emma Davis</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Meridian Group</t>
+          <t>Iris Group</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1357,52 +1365,52 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>233.1</v>
+        <v>1895.9</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>586.8</v>
+        <v>4946.4</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>58.5</v>
+        <v>374.4</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>140.5</v>
+        <v>891.4</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>111</v>
+        <v>234.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.798</v>
+        <v>0.342</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Robert Xu; Robert Hassan; Christopher Xu</t>
+          <t>James Davis; David Tanaka; Amanda Davis; Thomas Brown; Daniel Schmidt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Kepler Inc</t>
+          <t>Wavelength Networks</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1412,52 +1420,52 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2014-12-16</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2020-01-05</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>68.5</v>
+        <v>1705.8</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>204.6</v>
+        <v>5236</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>8.1</v>
+        <v>243.1</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>17.5</v>
+        <v>391.5</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>32.8</v>
+        <v>974.1</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.761</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Olivia Vega; Michael Qureshi; Robert Xu; Laura Evans; Elena Kim</t>
+          <t>Sophie Ivanov; Wei Anderson; Wei Yamamoto; James Kim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Atlas Energy</t>
+          <t>Tessera Logic</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1467,114 +1475,114 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>211.1</v>
+        <v>1704.6</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>371.1</v>
+        <v>3238</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>57.4</v>
+        <v>363.6</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>68.2</v>
+        <v>653.8</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>159.7</v>
+        <v>1283.6</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.473</v>
+        <v>0.952</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Laura Brown; Jessica Patel; Jessica Vega; Matthew Fischer</t>
+          <t>Matthew Vega; Christopher Anderson; Hannah Hassan; Emma Evans; Wei Rossi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Gravity Capital</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>2015-09-18</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2023-06-22</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1783.5</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>2588</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>261.4</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>221.8</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>739</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Schmidt; Sarah O'Brien; Olivia Xu; Christopher Tanaka; Yuki Fischer</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Fund D</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Fund D</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Umbra Foods</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>803.8</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>646</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Wei Hassan; Matthew Johnson; James Fischer; Ahmed Rossi</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Tessera Media</t>
+          <t>Glacier Pharma</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1584,42 +1592,42 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2017-10-14</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2023-12-30</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>973</v>
+        <v>464.3</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1017.7</v>
+        <v>1372.2</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>95.90000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>187.3</v>
+        <v>158.1</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>117.7</v>
+        <v>108.7</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.233</v>
+        <v>0.573</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Ravi Ueno; Emma Mueller; Andrew Rossi; Hannah Johnson</t>
+          <t>David Hassan; Sophie Fischer; Priya Nakamura; Jessica Brown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Lattice Health</t>
+          <t>Stratus Group</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1629,62 +1637,58 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2019-03-23</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
+          <t>2019-07-28</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="n">
-        <v>386.4</v>
+        <v>1552.5</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>535.9</v>
+        <v/>
       </c>
       <c r="I28" s="5" t="n">
-        <v>52.2</v>
+        <v>207.9</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>102.2</v>
+        <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>204.7</v>
+        <v>740.4</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.504</v>
+        <v>0.35</v>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Christopher Gupta; Daniel O'Brien; Elena Rossi</t>
+          <t>Elena Ueno; Amanda Nakamura</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Ember Systems</t>
+          <t>Atlas SA</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1694,107 +1698,59 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1377.7</v>
+        <v>397.5</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>3505.7</v>
+        <v>995.9</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>148.5</v>
+        <v>59.3</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>225.6</v>
+        <v>132.4</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>304.1</v>
+        <v>106.3</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.605</v>
+        <v>0.378</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Ravi Ivanov; Emma Williams; Jessica Johnson; Yuki Rossi; Emma Zhang</t>
+          <t>Sarah Ueno; Ravi Evans; Daniel Schmidt; Matthew Schmidt</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Meridian Foods</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>2017-03-20</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>559.8</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Sarah Nakamura; Wei Johnson; Mark Qureshi; James Davis; Olivia Evans</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Fund E</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Fathom Tech</t>
+          <t>Indigo Dynamics</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1804,114 +1760,154 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1490.6</v>
+        <v>942.6</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>2811.3</v>
+        <v>2468.9</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>378.6</v>
+        <v>85.3</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>312.3</v>
+        <v>138.8</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>686.3</v>
+        <v>261.8</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.797</v>
+        <v>0.573</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Michael Kim; Emma Anderson; David Yamamoto; Sophie Yamamoto</t>
+          <t>Ahmed Evans; James Xu</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Fund E</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Bloom Dynamics</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-04</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="n">
+        <v>1867.2</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>522.8</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>453.8</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Brown; Olivia Tanaka</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Ember Tech</t>
+          <t>Gravity Tech</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="n">
-        <v>173.3</v>
+        <v>746.5</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>148</v>
+        <v/>
       </c>
       <c r="I33" s="5" t="n">
-        <v>14.9</v>
+        <v>72.3</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>31.4</v>
+        <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>26.4</v>
+        <v>143.1</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.23</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Wei Davis; David Chen; Rachel Lopez</t>
+          <t>Sophie Davis; Daniel Johnson; Matthew Ivanov; Ahmed O'Brien; Amanda Chen</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Stratus Tech</t>
+          <t>Junction Health</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1921,52 +1917,52 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1700.2</v>
+        <v>1904.5</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>2878.4</v>
+        <v>2977.9</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>322</v>
+        <v>332.3</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>558.5</v>
+        <v>495.1</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>568.2</v>
+        <v>409.1</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.312</v>
+        <v>0.431</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Amanda Qureshi; Emma Schmidt</t>
+          <t>Olivia Ivanov; Jennifer Mueller; Hannah Ivanov</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Fathom Logistics</t>
+          <t>Quanta Ltd</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1976,52 +1972,52 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1876.4</v>
+        <v>602.3</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>6471.2</v>
+        <v>736.6</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>402.1</v>
+        <v>81.3</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>699.5</v>
+        <v>163.8</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>608.1</v>
+        <v>271.5</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.316</v>
+        <v>0.59</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Sophie Fischer; Amanda Zhang</t>
+          <t>Ravi Nakamura; Mark Lopez; Jennifer Chen</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Vertex Energy</t>
+          <t>Forge Networks</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2031,42 +2027,42 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2018-04-21</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>151</v>
+        <v>1481.5</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>299.8</v>
+        <v>1961.3</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>32.3</v>
+        <v>155.4</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>55.1</v>
+        <v>232.3</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>124.2</v>
+        <v>606.9</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.415</v>
+        <v>0.784</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Schmidt; Amanda Chen; Sarah Hassan</t>
+          <t>Laura Tanaka; Sarah Lopez; Amanda Mueller; Ravi Gupta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Forge AG</t>
+          <t>Yields AG</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2076,7 +2072,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2086,90 +2082,35 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>990.7</v>
+        <v>576.5</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1747</v>
+        <v>685.9</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>133.7</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>180.2</v>
+        <v>151.6</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>337.3</v>
+        <v>304.1</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.318</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Emma Hassan; Jessica Hassan; Wei O'Brien; Rachel Vega</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Cipher Health</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>2018-06-05</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>148.9</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>468.5</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Sarah Gupta; Rachel Xu</t>
+          <t>David Williams; Yuki Vega; Sarah O'Brien; Thomas Nakamura; Laura Williams</t>
         </is>
       </c>
     </row>
